--- a/data/trans_orig/P70A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P70A_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si dichos problemas de salud fueron causados por su trabajo en 2023</t>
+          <t>Población según si su ausencia en el trabajo por motivos de salud, fue debido a problemas de salud causados por su trabajo en 2023 (tasa de respuesta: 94,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41032</t>
+          <t>41333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57663</t>
+          <t>58115</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40524</t>
+          <t>40311</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51340</t>
+          <t>50701</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86257</t>
+          <t>86075</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105902</t>
+          <t>106056</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14618</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21520</t>
+          <t>22191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22053</t>
+          <t>22098</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>12217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>12860</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30961</t>
+          <t>30639</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>252642</t>
+          <t>250238</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355968</t>
+          <t>356146</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77593</t>
+          <t>76640</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92927</t>
+          <t>93581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>346055</t>
+          <t>344150</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>456268</t>
+          <t>456444</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40792</t>
+          <t>42882</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16726</t>
+          <t>17332</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51662</t>
+          <t>52706</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75855</t>
+          <t>73398</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79019</t>
+          <t>79946</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50788</t>
+          <t>51362</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68691</t>
+          <t>67916</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61338</t>
+          <t>60863</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75761</t>
+          <t>75589</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>118208</t>
+          <t>119657</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>140456</t>
+          <t>140937</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,24%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21799</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>11377</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28489</t>
+          <t>28950</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>14125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16175</t>
+          <t>16739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8565</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25130</t>
+          <t>25235</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88691</t>
+          <t>87955</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107869</t>
+          <t>108085</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77005</t>
+          <t>77715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93656</t>
+          <t>93619</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>170648</t>
+          <t>171315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>196862</t>
+          <t>196411</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22988</t>
+          <t>23816</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21927</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19992</t>
+          <t>19542</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39535</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18783</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12803</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26844</t>
+          <t>25788</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21305</t>
+          <t>21053</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39784</t>
+          <t>38650</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>466632</t>
+          <t>467555</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>606059</t>
+          <t>602534</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>271397</t>
+          <t>272838</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>301046</t>
+          <t>300493</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>759965</t>
+          <t>758757</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>921924</t>
+          <t>939866</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>16845</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>83324</t>
+          <t>82460</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30027</t>
+          <t>29604</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49106</t>
+          <t>49495</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>38175</t>
+          <t>32106</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>119360</t>
+          <t>119541</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94187</t>
+          <t>93105</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37210</t>
+          <t>37404</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61315</t>
+          <t>60292</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48195</t>
+          <t>43622</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>140240</t>
+          <t>141980</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P70A_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>50346</t>
+          <t>53637</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41333</t>
+          <t>44135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58115</t>
+          <t>61389</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>46457</t>
+          <t>51576</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40311</t>
+          <t>45325</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50701</t>
+          <t>56071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>96803</t>
+          <t>105213</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86075</t>
+          <t>93651</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106056</t>
+          <t>115323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15256</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11125</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>13971</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22191</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22098</t>
+          <t>23406</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>20625</t>
+          <t>21518</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>13644</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30639</t>
+          <t>31356</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71432</t>
+          <t>75411</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71432</t>
+          <t>75411</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71432</t>
+          <t>75411</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59967</t>
+          <t>65560</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59967</t>
+          <t>65560</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59967</t>
+          <t>65560</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>131399</t>
+          <t>140971</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131399</t>
+          <t>140971</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131399</t>
+          <t>140971</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>329667</t>
+          <t>99942</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>250238</t>
+          <t>86804</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>356146</t>
+          <t>109808</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>85773</t>
+          <t>95227</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76640</t>
+          <t>85520</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93581</t>
+          <t>102534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>415441</t>
+          <t>195169</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344150</t>
+          <t>181593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>456444</t>
+          <t>208954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>81,75%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11484</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42882</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11860</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>7214</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17332</t>
+          <t>18462</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>22520</t>
+          <t>24131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>16396</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>34179</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>21627</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>13887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73398</t>
+          <t>33417</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>14684</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>23756</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>35135</t>
+          <t>36312</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>26114</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79946</t>
+          <t>49368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>362501</t>
+          <t>133840</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>362501</t>
+          <t>133840</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>362501</t>
+          <t>133840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>110595</t>
+          <t>121771</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110595</t>
+          <t>121771</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110595</t>
+          <t>121771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>473096</t>
+          <t>255611</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>473096</t>
+          <t>255611</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>473096</t>
+          <t>255611</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60724</t>
+          <t>65722</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51362</t>
+          <t>56833</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67916</t>
+          <t>74008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>69825</t>
+          <t>79151</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60863</t>
+          <t>71254</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75589</t>
+          <t>85123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>130549</t>
+          <t>144874</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>119657</t>
+          <t>131471</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>140937</t>
+          <t>155458</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,85%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>20608</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19449</t>
+          <t>19607</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12151</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28950</t>
+          <t>29547</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>16339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16739</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15339</t>
+          <t>16592</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25235</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81273</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81273</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81273</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84064</t>
+          <t>93718</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>84064</t>
+          <t>93718</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>84064</t>
+          <t>93718</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>165337</t>
+          <t>181073</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>165337</t>
+          <t>181073</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>165337</t>
+          <t>181073</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>98792</t>
+          <t>102253</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87955</t>
+          <t>91087</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>108085</t>
+          <t>111132</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>86030</t>
+          <t>90899</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77715</t>
+          <t>82010</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93619</t>
+          <t>99890</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>184822</t>
+          <t>193152</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>171315</t>
+          <t>179026</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>196411</t>
+          <t>205822</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>15412</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23816</t>
+          <t>24981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15213</t>
+          <t>17385</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>24880</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>32797</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19542</t>
+          <t>22834</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>44840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19601</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>19918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12814</t>
+          <t>14060</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25788</t>
+          <t>27465</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>29456</t>
+          <t>31488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21053</t>
+          <t>22327</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38650</t>
+          <t>41961</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>123323</t>
+          <t>129236</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>123323</t>
+          <t>129236</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123323</t>
+          <t>129236</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>120049</t>
+          <t>128202</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>120049</t>
+          <t>128202</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>120049</t>
+          <t>128202</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>243372</t>
+          <t>257437</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>243372</t>
+          <t>257437</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>243372</t>
+          <t>257437</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>539529</t>
+          <t>321554</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>467555</t>
+          <t>302575</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>602534</t>
+          <t>339997</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>288086</t>
+          <t>316853</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>272838</t>
+          <t>301184</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>300493</t>
+          <t>332072</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>827615</t>
+          <t>638408</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>758757</t>
+          <t>612366</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>939866</t>
+          <t>662070</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>79,28%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45996</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16845</t>
+          <t>34965</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82460</t>
+          <t>63737</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>39038</t>
+          <t>42612</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29604</t>
+          <t>34185</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49495</t>
+          <t>56310</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>85034</t>
+          <t>90775</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>32106</t>
+          <t>73301</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>119541</t>
+          <t>107677</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>53004</t>
+          <t>56123</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>41392</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93105</t>
+          <t>71549</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>47551</t>
+          <t>49786</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37404</t>
+          <t>37426</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60292</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>100556</t>
+          <t>105910</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43622</t>
+          <t>88747</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141980</t>
+          <t>127695</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>638529</t>
+          <t>425841</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>638529</t>
+          <t>425841</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638529</t>
+          <t>425841</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>374675</t>
+          <t>409251</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>374675</t>
+          <t>409251</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>374675</t>
+          <t>409251</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1013204</t>
+          <t>835092</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1013204</t>
+          <t>835092</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1013204</t>
+          <t>835092</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
